--- a/rosnedra_forecast/rosnedra_forecast_conversion.xlsx
+++ b/rosnedra_forecast/rosnedra_forecast_conversion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://verdegcom-my.sharepoint.com/personal/s_osokin_verdeg_com/Documents/WORKS/VerdeG/2025/202503/20250327_rosnedra_forecast/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROG\QGIS\vgdb_tools\rosnedra_forecast\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="143" documentId="13_ncr:1_{D574C08A-5E69-4BB9-B9C6-DC582058975D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F0FA6EBB-8038-4CA7-A550-C0B1823661AE}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46AC0590-74F5-41FC-8CEC-0A48E53E7FC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1905" yWindow="1905" windowWidth="28800" windowHeight="15285" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Get Started with Python" sheetId="2" r:id="rId1"/>
@@ -4068,59 +4068,59 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="4"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="4"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -5503,26 +5503,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="24" x14ac:dyDescent="0.4">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="45" t="s">
         <v>255</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
     </row>
     <row r="3" spans="1:10" ht="24" x14ac:dyDescent="0.4">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="30" t="s">
         <v>254</v>
       </c>
-      <c r="B3" s="40"/>
-      <c r="C3" s="39"/>
-      <c r="G3" s="38" t="s">
+      <c r="B3" s="29"/>
+      <c r="C3" s="28"/>
+      <c r="G3" s="41" t="s">
         <v>253</v>
       </c>
-      <c r="H3" s="38"/>
+      <c r="H3" s="41"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
@@ -5540,16 +5540,16 @@
       <c r="E4" s="24" t="s">
         <v>248</v>
       </c>
-      <c r="G4" s="37" t="s">
+      <c r="G4" s="27" t="s">
         <v>247</v>
       </c>
-      <c r="H4" s="36" t="s">
+      <c r="H4" s="26" t="s">
         <v>246</v>
       </c>
-      <c r="I4" s="36" t="s">
+      <c r="I4" s="26" t="s">
         <v>245</v>
       </c>
-      <c r="J4" s="35" t="s">
+      <c r="J4" s="25" t="s">
         <v>244</v>
       </c>
     </row>
@@ -5569,17 +5569,17 @@
       <c r="E5" s="24" t="s">
         <v>233</v>
       </c>
-      <c r="G5" s="29" t="s">
+      <c r="G5" s="44" t="s">
         <v>243</v>
       </c>
-      <c r="H5" s="28" t="e" cm="1" vm="1">
+      <c r="H5" s="35" t="e" cm="1" vm="1">
         <f t="array" ref="H5">_xlfn._xlws.PY(0,1,IrisDataSet[#All])</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I5" s="27" t="s">
+      <c r="I5" s="36" t="s">
         <v>242</v>
       </c>
-      <c r="J5" s="32"/>
+      <c r="J5" s="37"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="24">
@@ -5597,10 +5597,10 @@
       <c r="E6" s="24" t="s">
         <v>233</v>
       </c>
-      <c r="G6" s="29"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="27"/>
-      <c r="J6" s="32"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="36"/>
+      <c r="J6" s="37"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="24">
@@ -5618,10 +5618,10 @@
       <c r="E7" s="24" t="s">
         <v>233</v>
       </c>
-      <c r="G7" s="29"/>
-      <c r="H7" s="28"/>
-      <c r="I7" s="27"/>
-      <c r="J7" s="32"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="35"/>
+      <c r="I7" s="36"/>
+      <c r="J7" s="37"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="24">
@@ -5639,10 +5639,10 @@
       <c r="E8" s="24" t="s">
         <v>233</v>
       </c>
-      <c r="G8" s="29"/>
-      <c r="H8" s="28"/>
-      <c r="I8" s="27"/>
-      <c r="J8" s="32"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="36"/>
+      <c r="J8" s="37"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="24">
@@ -5660,17 +5660,17 @@
       <c r="E9" s="24" t="s">
         <v>233</v>
       </c>
-      <c r="G9" s="33" t="s">
+      <c r="G9" s="43" t="s">
         <v>241</v>
       </c>
-      <c r="H9" s="28" t="e" cm="1" vm="2">
+      <c r="H9" s="35" t="e" cm="1" vm="2">
         <f t="array" ref="H9">_xlfn._xlws.PY(1,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I9" s="27" t="s">
+      <c r="I9" s="36" t="s">
         <v>240</v>
       </c>
-      <c r="J9" s="32"/>
+      <c r="J9" s="37"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="24">
@@ -5688,10 +5688,10 @@
       <c r="E10" s="24" t="s">
         <v>233</v>
       </c>
-      <c r="G10" s="29"/>
-      <c r="H10" s="28"/>
-      <c r="I10" s="27"/>
-      <c r="J10" s="32"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="35"/>
+      <c r="I10" s="36"/>
+      <c r="J10" s="37"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="24">
@@ -5709,10 +5709,10 @@
       <c r="E11" s="24" t="s">
         <v>233</v>
       </c>
-      <c r="G11" s="29"/>
-      <c r="H11" s="28"/>
-      <c r="I11" s="27"/>
-      <c r="J11" s="32"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="35"/>
+      <c r="I11" s="36"/>
+      <c r="J11" s="37"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="24">
@@ -5730,10 +5730,10 @@
       <c r="E12" s="24" t="s">
         <v>233</v>
       </c>
-      <c r="G12" s="29"/>
-      <c r="H12" s="28"/>
-      <c r="I12" s="27"/>
-      <c r="J12" s="32"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="35"/>
+      <c r="I12" s="36"/>
+      <c r="J12" s="37"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="24">
@@ -5751,17 +5751,17 @@
       <c r="E13" s="24" t="s">
         <v>233</v>
       </c>
-      <c r="G13" s="33" t="s">
+      <c r="G13" s="43" t="s">
         <v>239</v>
       </c>
-      <c r="H13" s="28" t="e" cm="1" vm="3">
+      <c r="H13" s="35" t="e" cm="1" vm="3">
         <f t="array" ref="H13">_xlfn._xlws.PY(2,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I13" s="27" t="s">
+      <c r="I13" s="36" t="s">
         <v>238</v>
       </c>
-      <c r="J13" s="34"/>
+      <c r="J13" s="42"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="24">
@@ -5779,10 +5779,10 @@
       <c r="E14" s="24" t="s">
         <v>233</v>
       </c>
-      <c r="G14" s="29"/>
-      <c r="H14" s="28"/>
-      <c r="I14" s="27"/>
-      <c r="J14" s="34"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="36"/>
+      <c r="J14" s="42"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="24">
@@ -5800,10 +5800,10 @@
       <c r="E15" s="24" t="s">
         <v>233</v>
       </c>
-      <c r="G15" s="29"/>
-      <c r="H15" s="28"/>
-      <c r="I15" s="27"/>
-      <c r="J15" s="34"/>
+      <c r="G15" s="44"/>
+      <c r="H15" s="35"/>
+      <c r="I15" s="36"/>
+      <c r="J15" s="42"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="24">
@@ -5821,10 +5821,10 @@
       <c r="E16" s="24" t="s">
         <v>233</v>
       </c>
-      <c r="G16" s="29"/>
-      <c r="H16" s="28"/>
-      <c r="I16" s="27"/>
-      <c r="J16" s="34"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="35"/>
+      <c r="I16" s="36"/>
+      <c r="J16" s="42"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="24">
@@ -5842,10 +5842,10 @@
       <c r="E17" s="24" t="s">
         <v>233</v>
       </c>
-      <c r="G17" s="29"/>
-      <c r="H17" s="28"/>
-      <c r="I17" s="27"/>
-      <c r="J17" s="34"/>
+      <c r="G17" s="44"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="36"/>
+      <c r="J17" s="42"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="24">
@@ -5863,17 +5863,17 @@
       <c r="E18" s="24" t="s">
         <v>233</v>
       </c>
-      <c r="G18" s="33" t="s">
+      <c r="G18" s="43" t="s">
         <v>237</v>
       </c>
-      <c r="H18" s="29" t="e" cm="1" vm="4">
+      <c r="H18" s="44" t="e" cm="1" vm="4">
         <f t="array" ref="H18">_xlfn._xlws.PY(3,0)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I18" s="27" t="s">
+      <c r="I18" s="36" t="s">
         <v>236</v>
       </c>
-      <c r="J18" s="32"/>
+      <c r="J18" s="37"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="24">
@@ -5891,10 +5891,10 @@
       <c r="E19" s="24" t="s">
         <v>233</v>
       </c>
-      <c r="G19" s="29"/>
-      <c r="H19" s="29"/>
-      <c r="I19" s="27"/>
-      <c r="J19" s="32"/>
+      <c r="G19" s="44"/>
+      <c r="H19" s="44"/>
+      <c r="I19" s="36"/>
+      <c r="J19" s="37"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="24">
@@ -5912,10 +5912,10 @@
       <c r="E20" s="24" t="s">
         <v>233</v>
       </c>
-      <c r="G20" s="29"/>
-      <c r="H20" s="29"/>
-      <c r="I20" s="27"/>
-      <c r="J20" s="32"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="44"/>
+      <c r="I20" s="36"/>
+      <c r="J20" s="37"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="24">
@@ -5933,10 +5933,10 @@
       <c r="E21" s="24" t="s">
         <v>233</v>
       </c>
-      <c r="G21" s="29"/>
-      <c r="H21" s="29"/>
-      <c r="I21" s="27"/>
-      <c r="J21" s="32"/>
+      <c r="G21" s="44"/>
+      <c r="H21" s="44"/>
+      <c r="I21" s="36"/>
+      <c r="J21" s="37"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="24">
@@ -5954,10 +5954,10 @@
       <c r="E22" s="24" t="s">
         <v>233</v>
       </c>
-      <c r="G22" s="29"/>
-      <c r="H22" s="29"/>
-      <c r="I22" s="27"/>
-      <c r="J22" s="32"/>
+      <c r="G22" s="44"/>
+      <c r="H22" s="44"/>
+      <c r="I22" s="36"/>
+      <c r="J22" s="37"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="24">
@@ -5975,10 +5975,10 @@
       <c r="E23" s="24" t="s">
         <v>233</v>
       </c>
-      <c r="G23" s="29"/>
-      <c r="H23" s="29"/>
-      <c r="I23" s="27"/>
-      <c r="J23" s="32"/>
+      <c r="G23" s="44"/>
+      <c r="H23" s="44"/>
+      <c r="I23" s="36"/>
+      <c r="J23" s="37"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="24">
@@ -5996,10 +5996,10 @@
       <c r="E24" s="24" t="s">
         <v>233</v>
       </c>
-      <c r="G24" s="29"/>
-      <c r="H24" s="29"/>
-      <c r="I24" s="27"/>
-      <c r="J24" s="32"/>
+      <c r="G24" s="44"/>
+      <c r="H24" s="44"/>
+      <c r="I24" s="36"/>
+      <c r="J24" s="37"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="24">
@@ -6017,10 +6017,10 @@
       <c r="E25" s="24" t="s">
         <v>233</v>
       </c>
-      <c r="G25" s="29"/>
-      <c r="H25" s="29"/>
-      <c r="I25" s="27"/>
-      <c r="J25" s="32"/>
+      <c r="G25" s="44"/>
+      <c r="H25" s="44"/>
+      <c r="I25" s="36"/>
+      <c r="J25" s="37"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="24">
@@ -6038,10 +6038,10 @@
       <c r="E26" s="24" t="s">
         <v>233</v>
       </c>
-      <c r="G26" s="29"/>
-      <c r="H26" s="29"/>
-      <c r="I26" s="27"/>
-      <c r="J26" s="32"/>
+      <c r="G26" s="44"/>
+      <c r="H26" s="44"/>
+      <c r="I26" s="36"/>
+      <c r="J26" s="37"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="24">
@@ -6059,17 +6059,17 @@
       <c r="E27" s="24" t="s">
         <v>233</v>
       </c>
-      <c r="G27" s="29" t="s">
+      <c r="G27" s="44" t="s">
         <v>235</v>
       </c>
-      <c r="H27" s="28" t="e" cm="1" vm="5">
+      <c r="H27" s="35" t="e" cm="1" vm="5">
         <f t="array" ref="H27">_xlfn._xlws.PY(4,0)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I27" s="27" t="s">
+      <c r="I27" s="36" t="s">
         <v>234</v>
       </c>
-      <c r="J27" s="31"/>
+      <c r="J27" s="38"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="24">
@@ -6087,10 +6087,10 @@
       <c r="E28" s="24" t="s">
         <v>233</v>
       </c>
-      <c r="G28" s="29"/>
-      <c r="H28" s="28"/>
-      <c r="I28" s="27"/>
-      <c r="J28" s="30"/>
+      <c r="G28" s="44"/>
+      <c r="H28" s="35"/>
+      <c r="I28" s="36"/>
+      <c r="J28" s="39"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="24">
@@ -6108,10 +6108,10 @@
       <c r="E29" s="24" t="s">
         <v>233</v>
       </c>
-      <c r="G29" s="29"/>
-      <c r="H29" s="28"/>
-      <c r="I29" s="27"/>
-      <c r="J29" s="30"/>
+      <c r="G29" s="44"/>
+      <c r="H29" s="35"/>
+      <c r="I29" s="36"/>
+      <c r="J29" s="39"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="24">
@@ -6129,10 +6129,10 @@
       <c r="E30" s="24" t="s">
         <v>233</v>
       </c>
-      <c r="G30" s="29"/>
-      <c r="H30" s="28"/>
-      <c r="I30" s="27"/>
-      <c r="J30" s="30"/>
+      <c r="G30" s="44"/>
+      <c r="H30" s="35"/>
+      <c r="I30" s="36"/>
+      <c r="J30" s="39"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="24">
@@ -6150,10 +6150,10 @@
       <c r="E31" s="24" t="s">
         <v>233</v>
       </c>
-      <c r="G31" s="29"/>
-      <c r="H31" s="28"/>
-      <c r="I31" s="27"/>
-      <c r="J31" s="30"/>
+      <c r="G31" s="44"/>
+      <c r="H31" s="35"/>
+      <c r="I31" s="36"/>
+      <c r="J31" s="39"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="24">
@@ -6171,10 +6171,10 @@
       <c r="E32" s="24" t="s">
         <v>233</v>
       </c>
-      <c r="G32" s="29"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="27"/>
-      <c r="J32" s="30"/>
+      <c r="G32" s="44"/>
+      <c r="H32" s="35"/>
+      <c r="I32" s="36"/>
+      <c r="J32" s="39"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="24">
@@ -6192,10 +6192,10 @@
       <c r="E33" s="24" t="s">
         <v>233</v>
       </c>
-      <c r="G33" s="29"/>
-      <c r="H33" s="28"/>
-      <c r="I33" s="27"/>
-      <c r="J33" s="30"/>
+      <c r="G33" s="44"/>
+      <c r="H33" s="35"/>
+      <c r="I33" s="36"/>
+      <c r="J33" s="39"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="24">
@@ -6213,10 +6213,10 @@
       <c r="E34" s="24" t="s">
         <v>233</v>
       </c>
-      <c r="G34" s="29"/>
-      <c r="H34" s="28"/>
-      <c r="I34" s="27"/>
-      <c r="J34" s="30"/>
+      <c r="G34" s="44"/>
+      <c r="H34" s="35"/>
+      <c r="I34" s="36"/>
+      <c r="J34" s="39"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="24">
@@ -6234,10 +6234,10 @@
       <c r="E35" s="24" t="s">
         <v>233</v>
       </c>
-      <c r="G35" s="29"/>
-      <c r="H35" s="28"/>
-      <c r="I35" s="27"/>
-      <c r="J35" s="30"/>
+      <c r="G35" s="44"/>
+      <c r="H35" s="35"/>
+      <c r="I35" s="36"/>
+      <c r="J35" s="39"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="24">
@@ -6255,10 +6255,10 @@
       <c r="E36" s="24" t="s">
         <v>233</v>
       </c>
-      <c r="G36" s="29"/>
-      <c r="H36" s="28"/>
-      <c r="I36" s="27"/>
-      <c r="J36" s="30"/>
+      <c r="G36" s="44"/>
+      <c r="H36" s="35"/>
+      <c r="I36" s="36"/>
+      <c r="J36" s="39"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="24">
@@ -6276,10 +6276,10 @@
       <c r="E37" s="24" t="s">
         <v>233</v>
       </c>
-      <c r="G37" s="29"/>
-      <c r="H37" s="28"/>
-      <c r="I37" s="27"/>
-      <c r="J37" s="30"/>
+      <c r="G37" s="44"/>
+      <c r="H37" s="35"/>
+      <c r="I37" s="36"/>
+      <c r="J37" s="39"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="24">
@@ -6297,10 +6297,10 @@
       <c r="E38" s="24" t="s">
         <v>233</v>
       </c>
-      <c r="G38" s="29"/>
-      <c r="H38" s="28"/>
-      <c r="I38" s="27"/>
-      <c r="J38" s="30"/>
+      <c r="G38" s="44"/>
+      <c r="H38" s="35"/>
+      <c r="I38" s="36"/>
+      <c r="J38" s="39"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="24">
@@ -6318,10 +6318,10 @@
       <c r="E39" s="24" t="s">
         <v>233</v>
       </c>
-      <c r="G39" s="29"/>
-      <c r="H39" s="28"/>
-      <c r="I39" s="27"/>
-      <c r="J39" s="30"/>
+      <c r="G39" s="44"/>
+      <c r="H39" s="35"/>
+      <c r="I39" s="36"/>
+      <c r="J39" s="39"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="24">
@@ -6339,10 +6339,10 @@
       <c r="E40" s="24" t="s">
         <v>233</v>
       </c>
-      <c r="G40" s="29"/>
-      <c r="H40" s="28"/>
-      <c r="I40" s="27"/>
-      <c r="J40" s="26"/>
+      <c r="G40" s="44"/>
+      <c r="H40" s="35"/>
+      <c r="I40" s="36"/>
+      <c r="J40" s="40"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="24">
@@ -8283,29 +8283,16 @@
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A155" s="25" t="s">
+      <c r="A155" s="46" t="s">
         <v>230</v>
       </c>
-      <c r="B155" s="25"/>
-      <c r="C155" s="25"/>
-      <c r="D155" s="25"/>
-      <c r="E155" s="25"/>
+      <c r="B155" s="46"/>
+      <c r="C155" s="46"/>
+      <c r="D155" s="46"/>
+      <c r="E155" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="H9:H12"/>
-    <mergeCell ref="I9:I12"/>
-    <mergeCell ref="J9:J12"/>
-    <mergeCell ref="J27:J40"/>
-    <mergeCell ref="H13:H17"/>
-    <mergeCell ref="I13:I17"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="J13:J17"/>
-    <mergeCell ref="G18:G26"/>
-    <mergeCell ref="H18:H26"/>
-    <mergeCell ref="I18:I26"/>
-    <mergeCell ref="J18:J26"/>
-    <mergeCell ref="J5:J8"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A155:E155"/>
     <mergeCell ref="G5:G8"/>
@@ -8316,6 +8303,19 @@
     <mergeCell ref="H27:H40"/>
     <mergeCell ref="I27:I40"/>
     <mergeCell ref="G9:G12"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="J13:J17"/>
+    <mergeCell ref="G18:G26"/>
+    <mergeCell ref="H18:H26"/>
+    <mergeCell ref="I18:I26"/>
+    <mergeCell ref="J18:J26"/>
+    <mergeCell ref="J5:J8"/>
+    <mergeCell ref="H9:H12"/>
+    <mergeCell ref="I9:I12"/>
+    <mergeCell ref="J9:J12"/>
+    <mergeCell ref="J27:J40"/>
+    <mergeCell ref="H13:H17"/>
+    <mergeCell ref="I13:I17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -8333,7 +8333,7 @@
     <col min="2" max="2" width="19.7109375"/>
     <col min="3" max="3" width="24.5703125"/>
     <col min="4" max="4" width="31.28515625"/>
-    <col min="5" max="5" width="38.5703125" customWidth="1"/>
+    <col min="5" max="5" width="79.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -8363,16 +8363,16 @@
       <c r="D2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="46" t="s">
+      <c r="E2" s="34" t="s">
         <v>264</v>
       </c>
-      <c r="F2" s="44" t="s">
+      <c r="F2" s="32" t="s">
         <v>259</v>
       </c>
-      <c r="G2" s="44" t="s">
+      <c r="G2" s="32" t="s">
         <v>261</v>
       </c>
-      <c r="H2" s="44" t="s">
+      <c r="H2" s="32" t="s">
         <v>263</v>
       </c>
     </row>
@@ -8396,7 +8396,7 @@
       <c r="F3" t="s">
         <v>260</v>
       </c>
-      <c r="G3" s="45" t="s">
+      <c r="G3" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H3" t="str">
@@ -8428,7 +8428,7 @@
       <c r="F4" t="s">
         <v>260</v>
       </c>
-      <c r="G4" s="45" t="s">
+      <c r="G4" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H4" t="str">
@@ -8464,7 +8464,7 @@
       <c r="F5" t="s">
         <v>260</v>
       </c>
-      <c r="G5" s="45" t="s">
+      <c r="G5" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H5" t="str">
@@ -8500,7 +8500,7 @@
       <c r="F6" t="s">
         <v>260</v>
       </c>
-      <c r="G6" s="45" t="s">
+      <c r="G6" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H6" t="str">
@@ -8536,7 +8536,7 @@
       <c r="F7" t="s">
         <v>260</v>
       </c>
-      <c r="G7" s="45" t="s">
+      <c r="G7" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H7" t="str">
@@ -8565,7 +8565,7 @@
       <c r="F8" t="s">
         <v>260</v>
       </c>
-      <c r="G8" s="45" t="s">
+      <c r="G8" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H8" t="str">
@@ -8594,7 +8594,7 @@
       <c r="F9" t="s">
         <v>260</v>
       </c>
-      <c r="G9" s="45" t="s">
+      <c r="G9" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H9" t="str">
@@ -8630,7 +8630,7 @@
       <c r="F10" t="s">
         <v>260</v>
       </c>
-      <c r="G10" s="45" t="s">
+      <c r="G10" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H10" t="str">
@@ -8665,7 +8665,7 @@
       <c r="F11" t="s">
         <v>260</v>
       </c>
-      <c r="G11" s="45" t="s">
+      <c r="G11" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H11" t="str">
@@ -8696,7 +8696,7 @@
       <c r="F12" t="s">
         <v>260</v>
       </c>
-      <c r="G12" s="45" t="s">
+      <c r="G12" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H12" t="str">
@@ -8725,7 +8725,7 @@
       <c r="F13" t="s">
         <v>260</v>
       </c>
-      <c r="G13" s="45" t="s">
+      <c r="G13" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H13" t="str">
@@ -8754,7 +8754,7 @@
       <c r="F14" t="s">
         <v>260</v>
       </c>
-      <c r="G14" s="45" t="s">
+      <c r="G14" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H14" t="str">
@@ -8783,7 +8783,7 @@
       <c r="F15" t="s">
         <v>260</v>
       </c>
-      <c r="G15" s="45" t="s">
+      <c r="G15" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H15" t="str">
@@ -8812,7 +8812,7 @@
       <c r="F16" t="s">
         <v>260</v>
       </c>
-      <c r="G16" s="45" t="s">
+      <c r="G16" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H16" t="str">
@@ -8842,7 +8842,7 @@
       <c r="F17" t="s">
         <v>260</v>
       </c>
-      <c r="G17" s="45" t="s">
+      <c r="G17" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H17" t="str">
@@ -8872,7 +8872,7 @@
       <c r="F18" t="s">
         <v>260</v>
       </c>
-      <c r="G18" s="45" t="s">
+      <c r="G18" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H18" t="str">
@@ -8902,7 +8902,7 @@
       <c r="F19" t="s">
         <v>260</v>
       </c>
-      <c r="G19" s="45" t="s">
+      <c r="G19" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H19" t="str">
@@ -8932,7 +8932,7 @@
       <c r="F20" t="s">
         <v>260</v>
       </c>
-      <c r="G20" s="45" t="s">
+      <c r="G20" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H20" t="str">
@@ -8962,7 +8962,7 @@
       <c r="F21" t="s">
         <v>260</v>
       </c>
-      <c r="G21" s="45" t="s">
+      <c r="G21" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H21" t="str">
@@ -8992,7 +8992,7 @@
       <c r="F22" t="s">
         <v>260</v>
       </c>
-      <c r="G22" s="45" t="s">
+      <c r="G22" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H22" t="str">
@@ -9022,7 +9022,7 @@
       <c r="F23" t="s">
         <v>260</v>
       </c>
-      <c r="G23" s="45" t="s">
+      <c r="G23" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H23" t="str">
@@ -9056,7 +9056,7 @@
       <c r="F24" t="s">
         <v>260</v>
       </c>
-      <c r="G24" s="45" t="s">
+      <c r="G24" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H24" t="str">
@@ -9085,7 +9085,7 @@
       <c r="F25" t="s">
         <v>260</v>
       </c>
-      <c r="G25" s="45" t="s">
+      <c r="G25" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H25" t="str">
@@ -9116,7 +9116,7 @@
       <c r="F26" t="s">
         <v>260</v>
       </c>
-      <c r="G26" s="45" t="s">
+      <c r="G26" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H26" t="str">
@@ -9146,7 +9146,7 @@
       <c r="F27" t="s">
         <v>260</v>
       </c>
-      <c r="G27" s="45" t="s">
+      <c r="G27" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H27" t="str">
@@ -9176,7 +9176,7 @@
       <c r="F28" t="s">
         <v>260</v>
       </c>
-      <c r="G28" s="45" t="s">
+      <c r="G28" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H28" t="str">
@@ -9205,7 +9205,7 @@
       <c r="F29" t="s">
         <v>260</v>
       </c>
-      <c r="G29" s="45" t="s">
+      <c r="G29" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H29" t="str">
@@ -9236,7 +9236,7 @@
       <c r="F30" t="s">
         <v>260</v>
       </c>
-      <c r="G30" s="45" t="s">
+      <c r="G30" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H30" t="str">
@@ -9269,7 +9269,7 @@
       <c r="F31" t="s">
         <v>260</v>
       </c>
-      <c r="G31" s="45" t="s">
+      <c r="G31" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H31" t="str">
@@ -9303,7 +9303,7 @@
       <c r="F32" t="s">
         <v>260</v>
       </c>
-      <c r="G32" s="45" t="s">
+      <c r="G32" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H32" t="str">
@@ -9334,7 +9334,7 @@
       <c r="F33" t="s">
         <v>260</v>
       </c>
-      <c r="G33" s="45" t="s">
+      <c r="G33" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H33" t="str">
@@ -9365,7 +9365,7 @@
       <c r="F34" t="s">
         <v>260</v>
       </c>
-      <c r="G34" s="45" t="s">
+      <c r="G34" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H34" t="str">
@@ -9400,7 +9400,7 @@
       <c r="F35" t="s">
         <v>260</v>
       </c>
-      <c r="G35" s="45" t="s">
+      <c r="G35" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H35" t="str">
@@ -9433,7 +9433,7 @@
       <c r="F36" t="s">
         <v>260</v>
       </c>
-      <c r="G36" s="45" t="s">
+      <c r="G36" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H36" t="str">
@@ -9468,7 +9468,7 @@
       <c r="F37" t="s">
         <v>260</v>
       </c>
-      <c r="G37" s="45" t="s">
+      <c r="G37" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H37" t="str">
@@ -9499,7 +9499,7 @@
       <c r="F38" t="s">
         <v>260</v>
       </c>
-      <c r="G38" s="45" t="s">
+      <c r="G38" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H38" t="str">
@@ -9532,7 +9532,7 @@
       <c r="F39" t="s">
         <v>260</v>
       </c>
-      <c r="G39" s="45" t="s">
+      <c r="G39" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H39" t="str">
@@ -9563,7 +9563,7 @@
       <c r="F40" t="s">
         <v>260</v>
       </c>
-      <c r="G40" s="45" t="s">
+      <c r="G40" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H40" t="str">
@@ -9594,7 +9594,7 @@
       <c r="F41" t="s">
         <v>260</v>
       </c>
-      <c r="G41" s="45" t="s">
+      <c r="G41" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H41" t="str">
@@ -9624,7 +9624,7 @@
       <c r="F42" t="s">
         <v>260</v>
       </c>
-      <c r="G42" s="45" t="s">
+      <c r="G42" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H42" t="str">
@@ -9655,7 +9655,7 @@
       <c r="F43" t="s">
         <v>260</v>
       </c>
-      <c r="G43" s="45" t="s">
+      <c r="G43" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H43" t="str">
@@ -9691,7 +9691,7 @@
       <c r="F44" t="s">
         <v>260</v>
       </c>
-      <c r="G44" s="45" t="s">
+      <c r="G44" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H44" t="str">
@@ -9720,7 +9720,7 @@
       <c r="F45" t="s">
         <v>260</v>
       </c>
-      <c r="G45" s="45" t="s">
+      <c r="G45" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H45" t="str">
@@ -9751,7 +9751,7 @@
       <c r="F46" t="s">
         <v>260</v>
       </c>
-      <c r="G46" s="45" t="s">
+      <c r="G46" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H46" t="str">
@@ -9781,7 +9781,7 @@
       <c r="F47" t="s">
         <v>260</v>
       </c>
-      <c r="G47" s="45" t="s">
+      <c r="G47" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H47" t="str">
@@ -9813,7 +9813,7 @@
       <c r="F48" t="s">
         <v>260</v>
       </c>
-      <c r="G48" s="45" t="s">
+      <c r="G48" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H48" t="str">
@@ -9843,7 +9843,7 @@
       <c r="F49" t="s">
         <v>260</v>
       </c>
-      <c r="G49" s="45" t="s">
+      <c r="G49" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H49" t="str">
@@ -9872,7 +9872,7 @@
       <c r="F50" t="s">
         <v>260</v>
       </c>
-      <c r="G50" s="45" t="s">
+      <c r="G50" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H50" t="str">
@@ -9903,7 +9903,7 @@
       <c r="F51" t="s">
         <v>260</v>
       </c>
-      <c r="G51" s="45" t="s">
+      <c r="G51" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H51" t="str">
@@ -9933,7 +9933,7 @@
       <c r="F52" t="s">
         <v>260</v>
       </c>
-      <c r="G52" s="45" t="s">
+      <c r="G52" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H52" t="str">
@@ -9946,7 +9946,7 @@
       <c r="A53" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="B53" s="43" t="s">
+      <c r="B53" s="31" t="s">
         <v>258</v>
       </c>
       <c r="C53" s="13" t="s">
@@ -9962,7 +9962,7 @@
       <c r="F53" t="s">
         <v>260</v>
       </c>
-      <c r="G53" s="45" t="s">
+      <c r="G53" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H53" t="str">
@@ -9979,7 +9979,7 @@
       <c r="A54" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="B54" s="43" t="s">
+      <c r="B54" s="31" t="s">
         <v>258</v>
       </c>
       <c r="C54" s="13" t="s">
@@ -9995,7 +9995,7 @@
       <c r="F54" t="s">
         <v>260</v>
       </c>
-      <c r="G54" s="45" t="s">
+      <c r="G54" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H54" t="str">
@@ -10012,7 +10012,7 @@
       <c r="A55" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B55" s="43" t="s">
+      <c r="B55" s="31" t="s">
         <v>258</v>
       </c>
       <c r="C55" s="13" t="s">
@@ -10028,7 +10028,7 @@
       <c r="F55" t="s">
         <v>260</v>
       </c>
-      <c r="G55" s="45" t="s">
+      <c r="G55" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H55" t="str">
@@ -10046,7 +10046,7 @@
       <c r="A56" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="B56" s="43" t="s">
+      <c r="B56" s="31" t="s">
         <v>258</v>
       </c>
       <c r="C56" s="13" t="s">
@@ -10062,7 +10062,7 @@
       <c r="F56" t="s">
         <v>260</v>
       </c>
-      <c r="G56" s="45" t="s">
+      <c r="G56" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H56" t="str">
@@ -10080,7 +10080,7 @@
       <c r="A57" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="B57" s="43" t="s">
+      <c r="B57" s="31" t="s">
         <v>258</v>
       </c>
       <c r="C57" s="13" t="s">
@@ -10096,7 +10096,7 @@
       <c r="F57" t="s">
         <v>260</v>
       </c>
-      <c r="G57" s="45" t="s">
+      <c r="G57" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H57" t="str">
@@ -10115,7 +10115,7 @@
       <c r="A58" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="B58" s="43" t="s">
+      <c r="B58" s="31" t="s">
         <v>258</v>
       </c>
       <c r="C58" s="13" t="s">
@@ -10131,7 +10131,7 @@
       <c r="F58" t="s">
         <v>260</v>
       </c>
-      <c r="G58" s="45" t="s">
+      <c r="G58" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H58" t="str">
@@ -10147,7 +10147,7 @@
       <c r="A59" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="B59" s="43" t="s">
+      <c r="B59" s="31" t="s">
         <v>258</v>
       </c>
       <c r="C59" s="8" t="s">
@@ -10163,7 +10163,7 @@
       <c r="F59" t="s">
         <v>260</v>
       </c>
-      <c r="G59" s="45" t="s">
+      <c r="G59" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H59" t="str">
@@ -10180,7 +10180,7 @@
       <c r="A60" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="B60" s="43" t="s">
+      <c r="B60" s="31" t="s">
         <v>258</v>
       </c>
       <c r="C60" s="8" t="s">
@@ -10196,7 +10196,7 @@
       <c r="F60" t="s">
         <v>260</v>
       </c>
-      <c r="G60" s="45" t="s">
+      <c r="G60" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H60" t="str">
@@ -10212,7 +10212,7 @@
       <c r="A61" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="B61" s="43" t="s">
+      <c r="B61" s="31" t="s">
         <v>258</v>
       </c>
       <c r="C61" s="13" t="s">
@@ -10228,7 +10228,7 @@
       <c r="F61" t="s">
         <v>260</v>
       </c>
-      <c r="G61" s="45" t="s">
+      <c r="G61" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H61" t="str">
@@ -10247,7 +10247,7 @@
       <c r="A62" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="B62" s="43" t="s">
+      <c r="B62" s="31" t="s">
         <v>258</v>
       </c>
       <c r="C62" s="20" t="s">
@@ -10263,7 +10263,7 @@
       <c r="F62" t="s">
         <v>260</v>
       </c>
-      <c r="G62" s="45" t="s">
+      <c r="G62" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H62" t="str">
@@ -10278,7 +10278,7 @@
       <c r="A63" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="B63" s="43" t="s">
+      <c r="B63" s="31" t="s">
         <v>258</v>
       </c>
       <c r="C63" s="8" t="s">
@@ -10294,7 +10294,7 @@
       <c r="F63" t="s">
         <v>260</v>
       </c>
-      <c r="G63" s="45" t="s">
+      <c r="G63" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H63" t="str">
@@ -10311,7 +10311,7 @@
       <c r="A64" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="B64" s="43" t="s">
+      <c r="B64" s="31" t="s">
         <v>258</v>
       </c>
       <c r="C64" s="13" t="s">
@@ -10327,7 +10327,7 @@
       <c r="F64" t="s">
         <v>260</v>
       </c>
-      <c r="G64" s="45" t="s">
+      <c r="G64" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H64" t="str">
@@ -10344,7 +10344,7 @@
       <c r="A65" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="B65" s="43" t="s">
+      <c r="B65" s="31" t="s">
         <v>258</v>
       </c>
       <c r="C65" s="13" t="s">
@@ -10360,7 +10360,7 @@
       <c r="F65" t="s">
         <v>260</v>
       </c>
-      <c r="G65" s="45" t="s">
+      <c r="G65" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H65" t="str">
@@ -10377,7 +10377,7 @@
       <c r="A66" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="B66" s="43" t="s">
+      <c r="B66" s="31" t="s">
         <v>258</v>
       </c>
       <c r="C66" s="13" t="s">
@@ -10393,7 +10393,7 @@
       <c r="F66" t="s">
         <v>260</v>
       </c>
-      <c r="G66" s="45" t="s">
+      <c r="G66" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H66" t="str">
@@ -10410,7 +10410,7 @@
       <c r="A67" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="B67" s="43" t="s">
+      <c r="B67" s="31" t="s">
         <v>258</v>
       </c>
       <c r="C67" s="13" t="s">
@@ -10426,7 +10426,7 @@
       <c r="F67" t="s">
         <v>260</v>
       </c>
-      <c r="G67" s="45" t="s">
+      <c r="G67" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H67" t="str">
@@ -10444,7 +10444,7 @@
       <c r="A68" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="B68" s="43" t="s">
+      <c r="B68" s="31" t="s">
         <v>258</v>
       </c>
       <c r="C68" s="13" t="s">
@@ -10460,7 +10460,7 @@
       <c r="F68" t="s">
         <v>260</v>
       </c>
-      <c r="G68" s="45" t="s">
+      <c r="G68" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H68" t="str">
@@ -10478,7 +10478,7 @@
       <c r="A69" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="B69" s="43" t="s">
+      <c r="B69" s="31" t="s">
         <v>258</v>
       </c>
       <c r="C69" s="16" t="s">
@@ -10494,11 +10494,11 @@
       <c r="F69" t="s">
         <v>260</v>
       </c>
-      <c r="G69" s="45" t="s">
+      <c r="G69" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H69" t="str">
-        <f t="shared" ref="H69:H74" si="1">CONCATENATE("(2025, '2025-01-15', '", B69, "', e'", C69, "', '", F69, "', e'", G69, "', e'", D69, "', '", E69, "'),")</f>
+        <f t="shared" ref="H69:H73" si="1">CONCATENATE("(2025, '2025-01-15', '", B69, "', e'", C69, "', '", F69, "', e'", G69, "', e'", D69, "', '", E69, "'),")</f>
         <v>(2025, '2025-01-15', 'Ханты-Мансийский автономный округ - Югра', e'ШугурСКИй Кондинский район', 'Прогнозный перечень участков недр углеводородного сырья, аукционы по которым планируется провести в 2025 году', e'https://rosnedra.gov.ru/activity/informatsionnye-resursy-i-programmy/prog2noznyy-perechen-uchastkov-nedr-uglevodorodnogo-syrya-auktsiony-po-kotorym-planiruetsya-provesti-/', e'нефть (извл,)
 D0 - 0,665 млн,т.
 D1 - 1,2 млн,т.
@@ -10512,7 +10512,7 @@
       <c r="A70" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="B70" s="43" t="s">
+      <c r="B70" s="31" t="s">
         <v>258</v>
       </c>
       <c r="C70" s="13" t="s">
@@ -10528,7 +10528,7 @@
       <c r="F70" t="s">
         <v>260</v>
       </c>
-      <c r="G70" s="45" t="s">
+      <c r="G70" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H70" t="str">
@@ -10547,7 +10547,7 @@
       <c r="A71" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="B71" s="43" t="s">
+      <c r="B71" s="31" t="s">
         <v>258</v>
       </c>
       <c r="C71" s="13" t="s">
@@ -10563,7 +10563,7 @@
       <c r="F71" t="s">
         <v>260</v>
       </c>
-      <c r="G71" s="45" t="s">
+      <c r="G71" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H71" t="str">
@@ -10596,7 +10596,7 @@
       <c r="F72" t="s">
         <v>260</v>
       </c>
-      <c r="G72" s="45" t="s">
+      <c r="G72" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H72" t="str">
@@ -10634,7 +10634,7 @@
       <c r="F73" t="s">
         <v>260</v>
       </c>
-      <c r="G73" s="45" t="s">
+      <c r="G73" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H73" t="str">
@@ -10663,7 +10663,7 @@
       <c r="F74" t="s">
         <v>260</v>
       </c>
-      <c r="G74" s="45" t="s">
+      <c r="G74" s="33" t="s">
         <v>262</v>
       </c>
       <c r="H74" t="str">
